--- a/docs/submission/sample-report.xlsx
+++ b/docs/submission/sample-report.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3055" uniqueCount="1035">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3057" uniqueCount="1036">
   <si>
     <t>Предварительная оценка роботизации</t>
   </si>
@@ -31,7 +31,7 @@
     <t>Проект</t>
   </si>
   <si>
-    <t>Склад организатора (демо)</t>
+    <t>Демо-склад</t>
   </si>
   <si>
     <t>Тип объекта</t>
@@ -43,7 +43,7 @@
     <t>Дата расчёта</t>
   </si>
   <si>
-    <t>25.09.2026 16:49 МСК</t>
+    <t>29.09.2026 15:12 МСК</t>
   </si>
   <si>
     <t>Модель расчёта</t>
@@ -61,7 +61,7 @@
     <t>Версия данных</t>
   </si>
   <si>
-    <t>7be2cba2</t>
+    <t>b97f38c0</t>
   </si>
   <si>
     <t>Вывод</t>
@@ -139,7 +139,7 @@
     <t>Интерпретация</t>
   </si>
   <si>
-    <t>базовый вариант</t>
+    <t>база сравнения</t>
   </si>
   <si>
     <t>средняя окупаемость (3–5 лет)</t>
@@ -148,7 +148,7 @@
     <t>быстрая окупаемость (менее 3 лет)</t>
   </si>
   <si>
-    <t>ROI по ТЗ</t>
+    <t>ROI валовый</t>
   </si>
   <si>
     <t>ROI чистый</t>
@@ -160,7 +160,7 @@
     <t>Дисконтированная окупаемость</t>
   </si>
   <si>
-    <t>не окупается в горизонте</t>
+    <t>не окупается за горизонт</t>
   </si>
   <si>
     <t>TCO за 5 лет</t>
@@ -190,10 +190,10 @@
     <t>16: Цена «AMR 1500 (грузоподъемность до 1 500 кг)» 2 200 000 ₽ не подтверждена производителем — уточните её по коммерческому предложению · «AMR 1500 (грузоподъемность до 1 500 кг)» в пилотной эксплуатации — серийных внедрений мало, характеристики могут измениться · и ещё 14</t>
   </si>
   <si>
-    <t>Базовый вариант (текущий процесс)</t>
-  </si>
-  <si>
-    <t>Не окупается в пределах горизонта</t>
+    <t>База сравнения</t>
+  </si>
+  <si>
+    <t>Не окупается за горизонт расчёта</t>
   </si>
   <si>
     <t>Окупается (NPV ≥ 0), но уступает рекомендуемому</t>
@@ -265,7 +265,7 @@
     <t>LABOR_SHARE_ESTIMATE</t>
   </si>
   <si>
-    <t>Доля труда, которую берут роботы (50 %), — оценка: в датасете её нет; диапазон 30–70 % входит в анализ чувствительности</t>
+    <t>Доля труда, которую берут роботы (50 %), — оценка: в исходных данных её нет; диапазон 30–70 % входит в анализ чувствительности</t>
   </si>
   <si>
     <t>ROUTE_ESTIMATE</t>
@@ -277,13 +277,13 @@
     <t>FLEET_COST_MISSING</t>
   </si>
   <si>
-    <t>Стоимость существующего парка погрузчиков в датасете не задана — эффект занижен, оценка консервативна</t>
+    <t>Стоимость существующего парка погрузчиков в исходных данных не задана — эффект занижен, оценка консервативна</t>
   </si>
   <si>
     <t>STAFF_REDUCTION</t>
   </si>
   <si>
-    <t>Высвобождение 11,9 FTE — учесть трудовые и социальные обязательства</t>
+    <t>Высвобождается ставок: 11,9 — учтите трудовые и социальные обязательства</t>
   </si>
   <si>
     <t>RAAS_LOWER_BOUND</t>
@@ -361,7 +361,7 @@
     <t>NPV меняет знак в пределах диапазона «Коэффициент загрузки» 70–85 %: от -236 460 ₽ до 7 888 415 ₽</t>
   </si>
   <si>
-    <t>Результат является предварительной оценкой и требует верификации при обследовании объекта.</t>
+    <t>Результат расчёта — предварительная оценка, его нужно проверить при обследовании объекта.</t>
   </si>
   <si>
     <t>Раздел</t>
@@ -379,7 +379,7 @@
     <t>По умолчанию</t>
   </si>
   <si>
-    <t>Диапазон организатора</t>
+    <t>Типовой диапазон</t>
   </si>
   <si>
     <t>Источник</t>
@@ -400,7 +400,7 @@
     <t>10 000–100 000 м²</t>
   </si>
   <si>
-    <t>Организатор, Датасеты_хакатон.xlsx › Склад › стр. 4</t>
+    <t>Базовые данные, Демо-набор данных › Склад › стр. 4</t>
   </si>
   <si>
     <t/>
@@ -412,7 +412,7 @@
     <t>5 000–50 000 м²</t>
   </si>
   <si>
-    <t>Организатор, Датасеты_хакатон.xlsx › Склад › стр. 5</t>
+    <t>Базовые данные, Демо-набор данных › Склад › стр. 5</t>
   </si>
   <si>
     <t>Высота потолков в зоне хранения</t>
@@ -424,7 +424,7 @@
     <t>5–16 м</t>
   </si>
   <si>
-    <t>Организатор, Датасеты_хакатон.xlsx › Склад › стр. 6</t>
+    <t>Базовые данные, Демо-набор данных › Склад › стр. 6</t>
   </si>
   <si>
     <t>Количество этажей (мезонинов)</t>
@@ -436,7 +436,7 @@
     <t>1–3 шт.</t>
   </si>
   <si>
-    <t>Организатор, Датасеты_хакатон.xlsx › Склад › стр. 7</t>
+    <t>Базовые данные, Демо-набор данных › Склад › стр. 7</t>
   </si>
   <si>
     <t>Ширина главных проездов</t>
@@ -445,7 +445,7 @@
     <t>2,5–6 м</t>
   </si>
   <si>
-    <t>Организатор, Датасеты_хакатон.xlsx › Склад › стр. 8</t>
+    <t>Базовые данные, Демо-набор данных › Склад › стр. 8</t>
   </si>
   <si>
     <t>Ширина рабочих проходов между стеллажами</t>
@@ -454,7 +454,7 @@
     <t>1,5–4,5 м</t>
   </si>
   <si>
-    <t>Организатор, Датасеты_хакатон.xlsx › Склад › стр. 9</t>
+    <t>Базовые данные, Демо-набор данных › Склад › стр. 9</t>
   </si>
   <si>
     <t>Тип напольного покрытия</t>
@@ -463,7 +463,7 @@
     <t>Промышленный бетон</t>
   </si>
   <si>
-    <t>Организатор, Датасеты_хакатон.xlsx › Склад › стр. 10</t>
+    <t>Базовые данные, Демо-набор данных › Склад › стр. 10</t>
   </si>
   <si>
     <t>Ровность пола (отклонение)</t>
@@ -475,7 +475,7 @@
     <t>1–8 мм/2 м</t>
   </si>
   <si>
-    <t>Организатор, Датасеты_хакатон.xlsx › Склад › стр. 11</t>
+    <t>Базовые данные, Демо-набор данных › Склад › стр. 11</t>
   </si>
   <si>
     <t>Режим работы</t>
@@ -490,7 +490,7 @@
     <t>1–3 смен</t>
   </si>
   <si>
-    <t>Организатор, Датасеты_хакатон.xlsx › Склад › стр. 13</t>
+    <t>Базовые данные, Демо-набор данных › Склад › стр. 13</t>
   </si>
   <si>
     <t>Рабочих дней в году</t>
@@ -502,7 +502,7 @@
     <t>365–365 дн.</t>
   </si>
   <si>
-    <t>Организатор, Датасеты_хакатон.xlsx › Склад › стр. 14</t>
+    <t>Базовые данные, Демо-набор данных › Склад › стр. 14</t>
   </si>
   <si>
     <t>Продолжительность смены</t>
@@ -514,7 +514,7 @@
     <t>10–11 ч</t>
   </si>
   <si>
-    <t>Организатор, Датасеты_хакатон.xlsx › Склад › стр. 15</t>
+    <t>Базовые данные, Демо-набор данных › Склад › стр. 15</t>
   </si>
   <si>
     <t>Пиковый коэффициент нагрузки</t>
@@ -523,7 +523,7 @@
     <t>1,2–2,5</t>
   </si>
   <si>
-    <t>Организатор, Датасеты_хакатон.xlsx › Склад › стр. 16</t>
+    <t>Базовые данные, Демо-набор данных › Склад › стр. 16</t>
   </si>
   <si>
     <t>Операции: объём и производительность</t>
@@ -538,13 +538,13 @@
     <t>500–5 000 поддон/сут</t>
   </si>
   <si>
-    <t>Организатор, Датасеты_хакатон.xlsx › Склад › стр. 18</t>
+    <t>Базовые данные, Демо-набор данных › Склад › стр. 18</t>
   </si>
   <si>
     <t>Объём отгрузки (поддоны/сутки)</t>
   </si>
   <si>
-    <t>Организатор, Датасеты_хакатон.xlsx › Склад › стр. 19</t>
+    <t>Базовые данные, Демо-набор данных › Склад › стр. 19</t>
   </si>
   <si>
     <t>Объём отбора (строк/сутки, всего)</t>
@@ -556,7 +556,7 @@
     <t>50 000–500 000 строк/сут</t>
   </si>
   <si>
-    <t>Организатор, Датасеты_хакатон.xlsx › Склад › стр. 20</t>
+    <t>Базовые данные, Демо-набор данных › Склад › стр. 20</t>
   </si>
   <si>
     <t>Объём отбора (штук/сутки, всего)</t>
@@ -568,7 +568,7 @@
     <t>75 000–750 000 шт./сут</t>
   </si>
   <si>
-    <t>Организатор, Датасеты_хакатон.xlsx › Склад › стр. 21</t>
+    <t>Базовые данные, Демо-набор данных › Склад › стр. 21</t>
   </si>
   <si>
     <t>Доля мелкоштучного отбора (piece-pick)</t>
@@ -580,7 +580,7 @@
     <t>10–80 %</t>
   </si>
   <si>
-    <t>Организатор, Датасеты_хакатон.xlsx › Склад › стр. 22</t>
+    <t>Базовые данные, Демо-набор данных › Склад › стр. 22</t>
   </si>
   <si>
     <t>Количество SKU (активных)</t>
@@ -592,7 +592,7 @@
     <t>1 000–10 000 SKU</t>
   </si>
   <si>
-    <t>Организатор, Датасеты_хакатон.xlsx › Склад › стр. 23</t>
+    <t>Базовые данные, Демо-набор данных › Склад › стр. 23</t>
   </si>
   <si>
     <t>Доля SKU с быстрым оборотом (A-класс)</t>
@@ -601,7 +601,7 @@
     <t>10–40 %</t>
   </si>
   <si>
-    <t>Организатор, Датасеты_хакатон.xlsx › Склад › стр. 24</t>
+    <t>Базовые данные, Демо-набор данных › Склад › стр. 24</t>
   </si>
   <si>
     <t>Персонал</t>
@@ -616,7 +616,7 @@
     <t>30–700 чел.</t>
   </si>
   <si>
-    <t>Организатор, Датасеты_хакатон.xlsx › Склад › стр. 26</t>
+    <t>Базовые данные, Демо-набор данных › Склад › стр. 26</t>
   </si>
   <si>
     <t>Из них: отборщики (комплектовщики)</t>
@@ -625,7 +625,7 @@
     <t>15–500 чел.</t>
   </si>
   <si>
-    <t>Организатор, Датасеты_хакатон.xlsx › Склад › стр. 27</t>
+    <t>Базовые данные, Демо-набор данных › Склад › стр. 27</t>
   </si>
   <si>
     <t>Из них: операторы погрузчиков</t>
@@ -634,7 +634,7 @@
     <t>5–80 чел.</t>
   </si>
   <si>
-    <t>Организатор, Датасеты_хакатон.xlsx › Склад › стр. 28</t>
+    <t>Базовые данные, Демо-набор данных › Склад › стр. 28</t>
   </si>
   <si>
     <t>Из них: операторы упаковочных линий</t>
@@ -643,7 +643,7 @@
     <t>5–60 чел.</t>
   </si>
   <si>
-    <t>Организатор, Датасеты_хакатон.xlsx › Склад › стр. 29</t>
+    <t>Базовые данные, Демо-набор данных › Склад › стр. 29</t>
   </si>
   <si>
     <t>Средняя з/п отборщика (gross)</t>
@@ -655,7 +655,7 @@
     <t>70 000–150 000 руб./мес.</t>
   </si>
   <si>
-    <t>Организатор, Датасеты_хакатон.xlsx › Склад › стр. 30</t>
+    <t>Базовые данные, Демо-набор данных › Склад › стр. 30</t>
   </si>
   <si>
     <t>Средняя з/п оператора погрузчика (gross)</t>
@@ -664,7 +664,7 @@
     <t>80 000–170 000 руб./мес.</t>
   </si>
   <si>
-    <t>Организатор, Датасеты_хакатон.xlsx › Склад › стр. 31</t>
+    <t>Базовые данные, Демо-набор данных › Склад › стр. 31</t>
   </si>
   <si>
     <t>Коэффициент начислений на ФОТ (страховые взносы)</t>
@@ -673,7 +673,7 @@
     <t>1,302–1,302</t>
   </si>
   <si>
-    <t>Организатор, Датасеты_хакатон.xlsx › Склад › стр. 32</t>
+    <t>Базовые данные, Демо-набор данных › Склад › стр. 32</t>
   </si>
   <si>
     <t>Средняя выработка отборщика (строк/ч)</t>
@@ -685,7 +685,7 @@
     <t>80–200 строк/ч·чел</t>
   </si>
   <si>
-    <t>Организатор, Датасеты_хакатон.xlsx › Склад › стр. 33</t>
+    <t>Базовые данные, Демо-набор данных › Склад › стр. 33</t>
   </si>
   <si>
     <t>Коэффициент потерь рабочего времени (отпуск, болезнь, текучесть)</t>
@@ -694,7 +694,7 @@
     <t>15–35 %</t>
   </si>
   <si>
-    <t>Организатор, Датасеты_хакатон.xlsx › Склад › стр. 34</t>
+    <t>Базовые данные, Демо-набор данных › Склад › стр. 34</t>
   </si>
   <si>
     <t>Маршруты и планировка</t>
@@ -706,7 +706,7 @@
     <t>15–60 м</t>
   </si>
   <si>
-    <t>Организатор, Датасеты_хакатон.xlsx › Склад › стр. 36</t>
+    <t>Базовые данные, Демо-набор данных › Склад › стр. 36</t>
   </si>
   <si>
     <t>Протяжённость конвейерной/транспортной системы</t>
@@ -715,7 +715,7 @@
     <t>0–2 000 м</t>
   </si>
   <si>
-    <t>Организатор, Датасеты_хакатон.xlsx › Склад › стр. 37</t>
+    <t>Базовые данные, Демо-набор данных › Склад › стр. 37</t>
   </si>
   <si>
     <t>Хранение и характеристики грузов</t>
@@ -727,7 +727,7 @@
     <t>Фронтальные паллетные</t>
   </si>
   <si>
-    <t>Организатор, Датасеты_хакатон.xlsx › Склад › стр. 39</t>
+    <t>Базовые данные, Демо-набор данных › Склад › стр. 39</t>
   </si>
   <si>
     <t>Количество паллетомест</t>
@@ -739,7 +739,7 @@
     <t>10 000–100 000 паллетомест</t>
   </si>
   <si>
-    <t>Организатор, Датасеты_хакатон.xlsx › Склад › стр. 40</t>
+    <t>Базовые данные, Демо-набор данных › Склад › стр. 40</t>
   </si>
   <si>
     <t>Средняя масса грузовой единицы (паллет)</t>
@@ -751,7 +751,7 @@
     <t>200–1 500 кг</t>
   </si>
   <si>
-    <t>Организатор, Датасеты_хакатон.xlsx › Склад › стр. 41</t>
+    <t>Базовые данные, Демо-набор данных › Склад › стр. 41</t>
   </si>
   <si>
     <t>Средняя масса штучной единицы (SKU)</t>
@@ -760,7 +760,7 @@
     <t>0,1–20 кг</t>
   </si>
   <si>
-    <t>Организатор, Датасеты_хакатон.xlsx › Склад › стр. 42</t>
+    <t>Базовые данные, Демо-набор данных › Склад › стр. 42</t>
   </si>
   <si>
     <t>Средние габариты паллеты (Д×Ш×В)</t>
@@ -772,7 +772,7 @@
     <t>мм</t>
   </si>
   <si>
-    <t>Организатор, Датасеты_хакатон.xlsx › Склад › стр. 43</t>
+    <t>Базовые данные, Демо-набор данных › Склад › стр. 43</t>
   </si>
   <si>
     <t>Средние габариты штучной единицы (Д×Ш×В)</t>
@@ -781,7 +781,7 @@
     <t>300×200×150</t>
   </si>
   <si>
-    <t>Организатор, Датасеты_хакатон.xlsx › Склад › стр. 44</t>
+    <t>Базовые данные, Демо-набор данных › Склад › стр. 44</t>
   </si>
   <si>
     <t>Доля негабаритных/нестандартных грузов</t>
@@ -790,7 +790,7 @@
     <t>0–30 %</t>
   </si>
   <si>
-    <t>Организатор, Датасеты_хакатон.xlsx › Склад › стр. 45</t>
+    <t>Базовые данные, Демо-набор данных › Склад › стр. 45</t>
   </si>
   <si>
     <t>Инфраструктура и ограничения</t>
@@ -805,7 +805,7 @@
     <t>100–3 000 кВт</t>
   </si>
   <si>
-    <t>Организатор, Датасеты_хакатон.xlsx › Склад › стр. 47</t>
+    <t>Базовые данные, Демо-набор данных › Склад › стр. 47</t>
   </si>
   <si>
     <t>Наличие WMS</t>
@@ -814,7 +814,7 @@
     <t>Да</t>
   </si>
   <si>
-    <t>Организатор, Датасеты_хакатон.xlsx › Склад › стр. 48</t>
+    <t>Базовые данные, Демо-набор данных › Склад › стр. 48</t>
   </si>
   <si>
     <t>Наличие ERP/1С</t>
@@ -823,7 +823,7 @@
     <t>1С:ERP</t>
   </si>
   <si>
-    <t>Организатор, Датасеты_хакатон.xlsx › Склад › стр. 49</t>
+    <t>Базовые данные, Демо-набор данных › Склад › стр. 49</t>
   </si>
   <si>
     <t>Планируемый бюджет на роботизацию (CAPEX)</t>
@@ -835,7 +835,7 @@
     <t>10–500 млн руб.</t>
   </si>
   <si>
-    <t>Организатор, Датасеты_хакатон.xlsx › Склад › стр. 50</t>
+    <t>Базовые данные, Демо-набор данных › Склад › стр. 50</t>
   </si>
   <si>
     <t>Горизонт расчёта окупаемости</t>
@@ -847,7 +847,7 @@
     <t>3–10 лет</t>
   </si>
   <si>
-    <t>Организатор, Датасеты_хакатон.xlsx › Склад › стр. 51</t>
+    <t>Базовые данные, Демо-набор данных › Склад › стр. 51</t>
   </si>
   <si>
     <t>Внутренние перемещения паллет (подпитка, перестановки)</t>
@@ -925,7 +925,7 @@
     <t>38 000–85 000 руб./мес.</t>
   </si>
   <si>
-    <t>Оценка, Датасеты_хакатон.xlsx › Аэропорт › стр. 34</t>
+    <t>Оценка, Демо-набор данных › Аэропорт › стр. 34</t>
   </si>
   <si>
     <t>Процесс</t>
@@ -970,7 +970,7 @@
     <t>Рекомендуется: лучший балл среди кандидатов с расчётом экономики — 72 из 100; Предназначен для процесса «Перемещение паллет: приёмка → хранение → отгрузка» на объекте типа «Склад»; Грузоподъёмность 1 500 кг ≥ масса груза 800 кг (запас 88 %); Минимальная ширина прохода 0,75 м ≤ ширина проходов объекта 2,8 м; Рабочая температура +5…+25 °C подходит для режима «Нормальный (+5…+25 °C)»</t>
   </si>
   <si>
-    <t>подъём на ярусы не предусмотрен: только горизонтальная транспортировка; размещение на верхние ярусы остаётся за погрузчиками; требует проверки: карточка собрана из нескольких строк каталога организатора; производительность не подтверждена первоисточником</t>
+    <t>подъём на ярусы не предусмотрен: только горизонтальная транспортировка; размещение на верхние ярусы остаётся за погрузчиками; требует проверки: карточка собрана из нескольких строк каталога; производительность не подтверждена первоисточником</t>
   </si>
   <si>
     <t>Экономика: 27,2 из 40 — Экономика: 27 из 40 — NPV покупки -4 108 652 ₽, третий среди 8 кандидатов; Данные: 4,9 из 20 — Данные: 5 из 20 — полнота карточки 94 % × подтверждено первоисточником 26 % характеристик; Зрелость: 15 из 15 — Зрелость: 15 из 15 — серийная эксплуатация; Запас: 15 из 15 — Запас: 15 из 15 — грузоподъёмность +88 % к массе груза (полный балл от +50 %); проход шире нужного на 2,05 м (полный балл от 1 м); Кейсы: 10 из 10 — Кейсы: 10 из 10 — есть опубликованные внедрения</t>
@@ -979,7 +979,7 @@
     <t>AMR 1500 (грузоподъемность до 1 500 кг)</t>
   </si>
   <si>
-    <t>Кандидат</t>
+    <t>Подходит</t>
   </si>
   <si>
     <t>Предназначен для процесса «Перемещение паллет: приёмка → хранение → отгрузка» на объекте типа «Склад»; Грузоподъёмность 1 500 кг ≥ масса груза 800 кг (запас 88 %); Минимальная ширина прохода 0,7 м ≤ ширина проходов объекта 2,8 м; Рабочая температура +5…+40 °C подходит для режима «Нормальный (+5…+25 °C)»</t>
@@ -1027,7 +1027,7 @@
     <t>Предназначен для процесса «Перемещение паллет: приёмка → хранение → отгрузка» на объекте типа «Склад»; Грузоподъёмность 2 000 кг ≥ масса груза 800 кг (запас 150 %); Минимальная ширина прохода 1,19 м ≤ ширина проходов объекта 2,8 м; Рабочая температура +5…+30 °C подходит для режима «Нормальный (+5…+25 °C)»</t>
   </si>
   <si>
-    <t>подъём на ярусы не предусмотрен: только горизонтальная транспортировка; размещение на верхние ярусы остаётся за погрузчиками; паспортная производительность не опубликована — в расчёт идёт цикл по скорости 1 м/с и планировке объекта; требует проверки: карточка собрана из нескольких строк каталога организатора; кейс внедрения не подтверждён</t>
+    <t>подъём на ярусы не предусмотрен: только горизонтальная транспортировка; размещение на верхние ярусы остаётся за погрузчиками; паспортная производительность не опубликована — в расчёт идёт цикл по скорости 1 м/с и планировке объекта; требует проверки: карточка собрана из нескольких строк каталога; кейс внедрения не подтверждён</t>
   </si>
   <si>
     <t>Экономика: 17,4 из 40 — Экономика: 17 из 40 — NPV покупки -21,0 млн ₽, шестой среди 8 кандидатов; Данные: 2,7 из 20 — Данные: 3 из 20 — полнота карточки 90 % × подтверждено первоисточником 15 % характеристик; Зрелость: 15 из 15 — Зрелость: 15 из 15 — серийная эксплуатация; Запас: 15 из 15 — Запас: 15 из 15 — грузоподъёмность +150 % к массе груза (полный балл от +50 %); проход шире нужного на 1,61 м (полный балл от 1 м); Кейсы: 10 из 10 — Кейсы: 10 из 10 — есть опубликованные внедрения</t>
@@ -1078,7 +1078,7 @@
     <t>перестройка стеллажей под каналы шаттла в CAPEX не учтена; требует проверки: производитель указан спорно; кейс внедрения не подтверждён; цена не подтверждена первоисточником; производительность не подтверждена первоисточником</t>
   </si>
   <si>
-    <t>Производительность: Укажите производительность вручную или выберите продукт с данными; Ставка RaaS: Услуга (RaaS) без ставки не рассчитывается: укажите ставку за робота в месяц (₽) или подставьте оценку по нормативу — она будет помечена как оценка</t>
+    <t>Производительность: Укажите производительность вручную или выберите решение с данными; Ставка RaaS: Услуга (RaaS) без ставки не рассчитывается: укажите ставку за робота в месяц (₽) или подставьте оценку по нормативу — она будет помечена как оценка</t>
   </si>
   <si>
     <t>Экономика: 0 из 40 — Экономика: 0 из 40 — нет данных для экономики: без производительности парк не посчитать; Данные: 1,9 из 20 — Данные: 2 из 20 — полнота карточки 74 % × подтверждено первоисточником 13 % характеристик; Зрелость: 15 из 15 — Зрелость: 15 из 15 — серийная эксплуатация; Запас: 15 из 15 — Запас: 15 из 15 — грузоподъёмность +88 % к массе груза (полный балл от +50 %); стационарное решение — проходы для проезда не нужны; Кейсы: 10 из 10 — Кейсы: 10 из 10 — есть опубликованные внедрения</t>
@@ -1093,7 +1093,7 @@
     <t>высота подъёма не опубликована — размещение на ярус 9 м требует проверки; пилотная эксплуатация; требует проверки: производитель указан спорно; цена не подтверждена первоисточником</t>
   </si>
   <si>
-    <t>Производительность: Укажите производительность вручную или выберите продукт с данными; Ставка RaaS: Услуга (RaaS) без ставки не рассчитывается: укажите ставку за робота в месяц (₽) или подставьте оценку по нормативу — она будет помечена как оценка; Ширина прохода: Уточните у производителя минимальную ширину прохода и разворота — без неё не проверить проходы объекта 2,8 м</t>
+    <t>Производительность: Укажите производительность вручную или выберите решение с данными; Ставка RaaS: Услуга (RaaS) без ставки не рассчитывается: укажите ставку за робота в месяц (₽) или подставьте оценку по нормативу — она будет помечена как оценка; Ширина прохода: Уточните у производителя минимальную ширину прохода и разворота — без неё не проверить проходы объекта 2,8 м</t>
   </si>
   <si>
     <t>Экономика: 0 из 40 — Экономика: 0 из 40 — нет данных для экономики: без производительности парк не посчитать; Данные: 0 из 20 — Данные: 0 из 20 — полнота карточки 65 % × подтверждено первоисточником 0 % характеристик; Зрелость: 9 из 15 — Зрелость: 9 из 15 — пилотная эксплуатация — засчитывается 0,6 от серийной; Запас: 7,5 из 15 — Запас: 8 из 15 — грузоподъёмность +150 % к массе груза (полный балл от +50 %); ширина прохода не опубликована — засчитано 0,5; Кейсы: 10 из 10 — Кейсы: 10 из 10 — есть опубликованные внедрения</t>
@@ -1147,13 +1147,13 @@
     <t>DMR 600 (грузоподъемность до 600 кг): грузоподъёмность 600 кг &lt; масса груза 800 кг</t>
   </si>
   <si>
-    <t>подъём на ярусы не предусмотрен: только горизонтальная транспортировка; размещение на верхние ярусы остаётся за погрузчиками; пилотная эксплуатация; требует проверки: карточка собрана из нескольких строк каталога организатора; цена не подтверждена первоисточником</t>
+    <t>подъём на ярусы не предусмотрен: только горизонтальная транспортировка; размещение на верхние ярусы остаётся за погрузчиками; пилотная эксплуатация; требует проверки: карточка собрана из нескольких строк каталога; цена не подтверждена первоисточником</t>
   </si>
   <si>
     <t>Ronavi RCM (грузоподъемность до 350 кг)</t>
   </si>
   <si>
-    <t>Статус НИОКР — в расчёт не включается; Модель не найдена у производителя; Опытный образец; Модель Ronavi RCM не найдена у производителя: в каталоге ronavi-robotics.ru семь моделей, страница /catalogue/rcm отвечает 404 (проверено 2026-09-23); Ronavi RCM (грузоподъемность до 350 кг): грузоподъёмность 350 кг &lt; масса груза 800 кг</t>
+    <t>Статус НИОКР — в расчёт не включается; Модель не найдена у производителя; Опытный образец; Модель Ronavi RCM не найдена у производителя: в каталоге ronavi-robotics.ru семь моделей, страница /catalogue/rcm недоступна (проверено 23.09.2026); Ronavi RCM (грузоподъемность до 350 кг): грузоподъёмность 350 кг &lt; масса груза 800 кг</t>
   </si>
   <si>
     <t>подъём на ярусы не предусмотрен: только горизонтальная транспортировка; размещение на верхние ярусы остаётся за погрузчиками; требует проверки: цена не подтверждена первоисточником; полнота карточки 39 % (меньше 60 %)</t>
@@ -1162,7 +1162,7 @@
     <t>Tagarka (грузоподъемность до 35 000 кг)</t>
   </si>
   <si>
-    <t>Вариант не опубликован; Вариант Tagarka 35 т не опубликован производителем: на сайте Семаргл линейка 2 / 6 / 9 т, большие грузоподъёмности — только под заказ (проверено 2026-09-23)</t>
+    <t>Вариант не опубликован; Вариант Tagarka 35 т не опубликован производителем: на сайте Семаргл линейка 2 / 6 / 9 т, большие грузоподъёмности — только под заказ (проверено 23.09.2026)</t>
   </si>
   <si>
     <t>Автоматизированное хранение</t>
@@ -1273,7 +1273,7 @@
     <t>пилотная эксплуатация; требует проверки: цена не подтверждена первоисточником; полнота карточки 55 % (меньше 60 %)</t>
   </si>
   <si>
-    <t>Производительность: Укажите производительность вручную или выберите продукт с данными; Ставка RaaS: Услуга (RaaS) без ставки не рассчитывается: укажите ставку за робота в месяц (₽) или подставьте оценку по нормативу — она будет помечена как оценка; Грузоподъёмность: Уточните грузоподъёмность у производителя — без неё не проверить, повезёт ли робот груз 1,8 кг</t>
+    <t>Производительность: Укажите производительность вручную или выберите решение с данными; Ставка RaaS: Услуга (RaaS) без ставки не рассчитывается: укажите ставку за робота в месяц (₽) или подставьте оценку по нормативу — она будет помечена как оценка; Грузоподъёмность: Уточните грузоподъёмность у производителя — без неё не проверить, повезёт ли робот груз 1,8 кг</t>
   </si>
   <si>
     <t>Экономика: 0 из 40 — Экономика: 0 из 40 — нет данных для экономики: экономика процесса «Штучный отбор (товар к человеку)» в прототипе не рассчитывается; Данные: 0,7 из 20 — Данные: 1 из 20 — полнота карточки 55 % × подтверждено первоисточником 6 % характеристик; Зрелость: 9 из 15 — Зрелость: 9 из 15 — пилотная эксплуатация — засчитывается 0,6 от серийной; Запас: 7,5 из 15 — Запас: 8 из 15 — грузоподъёмность не опубликована — засчитано 0,5; ширина проходов процессом не ограничивается; Кейсы: 10 из 10 — Кейсы: 10 из 10 — есть опубликованные внедрения</t>
@@ -1282,7 +1282,7 @@
     <t>Робот-комплектовщик</t>
   </si>
   <si>
-    <t>Статус НИОКР — в расчёт не включается; Опытный образец; Статус «НИОКР» в каталоге организатора — опытный образец, в расчёт не включается</t>
+    <t>Статус НИОКР — в расчёт не включается; Опытный образец; Статус «НИОКР» в каталоге — опытный образец, в расчёт не включается</t>
   </si>
   <si>
     <t>требует проверки: цена похожа на условную (типовое значение каталога); цена не подтверждена первоисточником; полнота карточки 52 % (меньше 60 %)</t>
@@ -1333,7 +1333,7 @@
     <t>требует проверки: цена может быть годовой подпиской, а не ценой покупки; цена не подтверждена первоисточником</t>
   </si>
   <si>
-    <t>Производительность: Укажите производительность вручную или выберите продукт с данными; Ширина прохода: Уточните у производителя минимальную ширину прохода и разворота — без неё не проверить проходы объекта 2,8 м</t>
+    <t>Производительность: Укажите производительность вручную или выберите решение с данными; Ширина прохода: Уточните у производителя минимальную ширину прохода и разворота — без неё не проверить проходы объекта 2,8 м</t>
   </si>
   <si>
     <t>MARK 2 SE</t>
@@ -1531,13 +1531,13 @@
     <t>Оборудование (роботы)</t>
   </si>
   <si>
-    <t>N × цена за единицу</t>
+    <t>N × цена робота</t>
   </si>
   <si>
     <t>11 × 2 700 000 ₽</t>
   </si>
   <si>
-    <t>Организатор</t>
+    <t>Базовые данные</t>
   </si>
   <si>
     <t>Зарядные станции</t>
@@ -1624,7 +1624,7 @@
     <t>11 × 2 200 000 ₽</t>
   </si>
   <si>
-    <t>Организатор (цена не подтверждена производителем)</t>
+    <t>Базовые данные (цена не подтверждена производителем)</t>
   </si>
   <si>
     <t>2 × 300 000 ₽</t>
@@ -1642,7 +1642,7 @@
     <t>10 % × 29 800 000 ₽</t>
   </si>
   <si>
-    <t>ФОТ персонала процессов (как есть)</t>
+    <t>ФОТ персонала процессов («Как есть»)</t>
   </si>
   <si>
     <t>Σ численность × c по процессам охвата сравнения</t>
@@ -1822,7 +1822,7 @@
     <t>Окупаемость, ROI, NPV</t>
   </si>
   <si>
-    <t>не применимо: базовый сценарий без вложений</t>
+    <t>не применимо: сценарий «Как есть» без вложений</t>
   </si>
   <si>
     <t>TCO за 5 лет, ₽</t>
@@ -1837,10 +1837,10 @@
     <t>Простой срок окупаемости, лет</t>
   </si>
   <si>
-    <t>ROI по ТЗ за 5 лет, %</t>
-  </si>
-  <si>
-    <t>ROI чистый (ROI по ТЗ − 100 %), %</t>
+    <t>ROI валовый за 5 лет, %</t>
+  </si>
+  <si>
+    <t>ROI чистый (ROI валовый − 100 %), %</t>
   </si>
   <si>
     <t>NPV за 5 лет, ₽</t>
@@ -1897,7 +1897,7 @@
     <t>Численность операторов погрузчиков</t>
   </si>
   <si>
-    <t>организатор</t>
+    <t>типовой диапазон</t>
   </si>
   <si>
     <t>Горизонт расчёта</t>
@@ -2005,10 +2005,10 @@
     <t>Обслужено заданий пика, %</t>
   </si>
   <si>
-    <t>Минимальный парк по имитации</t>
-  </si>
-  <si>
-    <t>Парк по норме организатора</t>
+    <t>Минимальный устойчивый парк</t>
+  </si>
+  <si>
+    <t>Парк по паспортной норме</t>
   </si>
   <si>
     <t>нет нормы</t>
@@ -2056,10 +2056,10 @@
     <t>utilization</t>
   </si>
   <si>
-    <t>Организатор задаёт типовой KPI загрузки AMR 70–85 % и оговаривает, что он уже учитывает зарядку, простои и ожидание. Середина диапазона 0,775 — наш выбор внутри интервала организатора; границы 0,70 и 0,85 используются в анализе чувствительности.</t>
-  </si>
-  <si>
-    <t>Датасеты_хакатон.xlsx › легенда «Коэффициент загрузки AMR» 70–85 %</t>
+    <t>Легенда демо-набора задаёт типовой KPI загрузки AMR 70–85 % и оговаривает, что он уже учитывает зарядку, простои и ожидание. Середина диапазона 0,775 — наш выбор внутри этого интервала; границы 0,70 и 0,85 используются в анализе чувствительности.</t>
+  </si>
+  <si>
+    <t>Демо-набор данных › легенда «Коэффициент загрузки AMR» 70–85 %</t>
   </si>
   <si>
     <t>Коэффициент доступности робота</t>
@@ -2068,10 +2068,10 @@
     <t>availability</t>
   </si>
   <si>
-    <t>Загрузка организатора уже учитывает зарядку и простои — без двойного учёта. Поэтому доступность по умолчанию равна 1; снижать её имеет смысл только при известных простоях сверх тех, что заложены в загрузку (например, плановое ТО в рабочие смены).</t>
-  </si>
-  <si>
-    <t>Формула: 1 (простои и зарядка уже внутри коэффициента загрузки организатора)</t>
+    <t>Типовая загрузка уже учитывает зарядку и простои. Чтобы не учесть их дважды, доступность по умолчанию равна 1; снижать её имеет смысл только при известных простоях сверх тех, что заложены в загрузку (например, плановое обслуживание в рабочие смены).</t>
+  </si>
+  <si>
+    <t>Формула: 1 (простои и зарядка уже внутри типового коэффициента загрузки)</t>
   </si>
   <si>
     <t>Резерв парка сверх пиковой потребности</t>
@@ -2080,10 +2080,10 @@
     <t>reservePct</t>
   </si>
   <si>
-    <t>Организатор требует рассчитывать роботов на пиковую нагрузку с резервом 15–20 %. Середина 17,5 % — наш выбор внутри интервала организатора.</t>
-  </si>
-  <si>
-    <t>Датасеты_хакатон.xlsx › легенда «Пиковая нагрузка» резерв 15–20 %</t>
+    <t>Легенда демо-набора требует рассчитывать роботов на пиковую нагрузку с резервом 15–20 %. Середина 17,5 % — наш выбор внутри этого интервала.</t>
+  </si>
+  <si>
+    <t>Демо-набор данных › легенда «Пиковая нагрузка» резерв 15–20 %</t>
   </si>
   <si>
     <t>Доля скорости при движении с грузом</t>
@@ -2131,7 +2131,7 @@
     <t>chargerSafetyFactor</t>
   </si>
   <si>
-    <t>Роботы уходят на зарядку не строго по очереди: несколько машин могут разрядиться одновременно. Средняя доля времени на зарядке умножается на 1,5, чтобы очередь к станциям не становилась узким местом; значение проверяется имитацией (узкое место charging).</t>
+    <t>Роботы уходят на зарядку не строго по очереди: несколько из них могут разрядиться одновременно. Средняя доля времени на зарядке умножается на 1,5, чтобы очередь к станциям не становилась узким местом; значение проверяется имитацией (узкое место «зарядные станции»).</t>
   </si>
   <si>
     <t>Роботов на одну зарядную станцию (если нет данных о зарядке)</t>
@@ -2149,7 +2149,7 @@
     <t>chargerPowerKw</t>
   </si>
   <si>
-    <t>Нужна только для проверки лимита электроснабжения объекта (риск POWER: станции × мощность &gt; доступной мощности). Паспортная мощность станций в найденных данных не публикуется, 3 кВт — оценка порядка величины.</t>
+    <t>Нужна только для проверки лимита электроснабжения объекта (если станции × мощность &gt; доступной мощности, в рисках сценария появляется предупреждение). Паспортная мощность станций в найденных данных не публикуется, 3 кВт — оценка порядка величины.</t>
   </si>
   <si>
     <t>Труд</t>
@@ -2161,10 +2161,10 @@
     <t>payrollMultiplier</t>
   </si>
   <si>
-    <t>Коэффициент начислений 30,2 % (страховые взносы, стандартная ставка 2024–2025) задан организатором и зафиксирован во всех трёх датасетах (min = max), поэтому не редактируется.</t>
-  </si>
-  <si>
-    <t>Датасеты_хакатон.xlsx › легенда «ФОТ» 30,2 %</t>
+    <t>Коэффициент начислений 30,2 % (страховые взносы, стандартная ставка 2024–2025) задан в демо-наборе и фиксирован для всех трёх типов объектов, поэтому не редактируется.</t>
+  </si>
+  <si>
+    <t>Демо-набор данных › легенда «ФОТ» 30,2 %</t>
   </si>
   <si>
     <t>Доля труда процесса, которую берут роботы</t>
@@ -2173,7 +2173,7 @@
     <t>laborShareAutomatable</t>
   </si>
   <si>
-    <t>Роботы берут горизонтальную транспортировку; размещение на верхние ярусы при потолке 10 м остаётся за погрузчиками. Какую долю работы водителей погрузчиков составляет горизонтальная перевозка, в датасете нет, поэтому 0,5 — оценка, а диапазон 0,3–0,7 входит в анализ чувствительности.</t>
+    <t>Роботы берут горизонтальную транспортировку; размещение на верхние ярусы при потолке 10 м остаётся за погрузчиками. Какую долю работы водителей погрузчиков составляет горизонтальная перевозка, в исходных данных нет, поэтому 0,5 — оценка, а диапазон 0,3–0,7 входит в анализ чувствительности.</t>
   </si>
   <si>
     <t>Роботов на один пост диспетчера парка</t>
@@ -2200,10 +2200,10 @@
     <t>capexReservePct</t>
   </si>
   <si>
-    <t>Организатор включает в CAPEX резерв 10 %. Мы читаем его как 10 % от суммы остальных статей и показываем это в расчёте. Диапазон 5–20 % — наш, он ограничивает правку администратором.</t>
-  </si>
-  <si>
-    <t>Датасеты_хакатон.xlsx › легенда «CAPEX» резерв 10 %</t>
+    <t>Легенда демо-набора включает в CAPEX резерв 10 %. Мы читаем его как 10 % от суммы остальных статей и показываем это в расчёте. Диапазон 5–20 % — наш, он ограничивает правку администратором.</t>
+  </si>
+  <si>
+    <t>Демо-набор данных › легенда «CAPEX» резерв 10 %</t>
   </si>
   <si>
     <t>ПО управления парком (разово на объект)</t>
@@ -2236,7 +2236,7 @@
     <t>commissioningRubPerUnit</t>
   </si>
   <si>
-    <t>Вейбот Роботикс публикует «Пусконаладка от 100 000 ₽ для Cleanbotics 400 PRO и от 150 000 ₽ для Cleanbotics 600». Берём нижнюю опубликованную цену на единицу; для складских AMR это аналог, цена конкретного интегратора может быть выше.</t>
+    <t>Вейбот Роботикс публикует «Пусконаладка от 100 000 ₽ для Cleanbotics 400 PRO и от 150 000 ₽ для Cleanbotics 600». Берём нижнюю опубликованную цену пусконаладки за робота; для складских AMR это аналог, цена конкретного интегратора может быть выше.</t>
   </si>
   <si>
     <t>Вейбот Роботикс (Клинботикс), страница «Покупка и аренда»; https://waybotrobotics.com/buy-rent</t>
@@ -2257,10 +2257,10 @@
     <t>chargerRub</t>
   </si>
   <si>
-    <t>Ronavi в статье о стоимости владения: «зарядные станции (200−400 тыс. рублей каждая)». Середина 300 000 ₽ — наш выбор внутри опубликованного диапазона; дилер Stellmart продаёт станцию Ronavi Charger «от 360 000 руб.» (https://stellmart.ru/logisticheskie-roboty/ronavi-h1500/). Та же статья называет цену H1500 «около 2-3 млн рублей при покупке с учетом зарядных станций и прочей инфраструктуры», а у дилера робот («от 2 700 000 руб.», как в каталоге организатора) и станция продаются отдельно. Поэтому станции — отдельная строка CAPEX; входят ли они в цену робота, проверяется по коммерческому предложению.</t>
-  </si>
-  <si>
-    <t>Ronavi Robotics, статья «Как считать стоимость владения (TCO)» (ссылка в sourceUrl); дилер Stellmart, карточка Ronavi H1500 — https://stellmart.ru/logisticheskie-roboty/ronavi-h1500/; https://ronavi-robotics.ru/media/tpost/l8s0fty3m1-kak-schitat-stoimost-vladeniya-tco-logis</t>
+    <t>Ronavi в статье о стоимости владения: «зарядные станции (200−400 тыс. рублей каждая)». Середина 300 000 ₽ — наш выбор внутри опубликованного диапазона; дилер Stellmart продаёт станцию Ronavi Charger «от 360 000 руб.» (https://stellmart.ru/logisticheskie-roboty/ronavi-h1500/). Та же статья называет цену H1500 «около 2-3 млн рублей при покупке с учетом зарядных станций и прочей инфраструктуры», а у дилера робот («от 2 700 000 руб.», как в каталоге) и станция продаются отдельно. Поэтому станции — отдельная строка CAPEX; входят ли они в цену робота, проверяется по коммерческому предложению.</t>
+  </si>
+  <si>
+    <t>Ronavi Robotics, статья «Как считать стоимость владения (TCO)»; дилер Stellmart, карточка Ronavi H1500 — https://stellmart.ru/logisticheskie-roboty/ronavi-h1500/; https://ronavi-robotics.ru/media/tpost/l8s0fty3m1-kak-schitat-stoimost-vladeniya-tco-logis</t>
   </si>
   <si>
     <t>Инфраструктура площадки на 1 м² активной зоны</t>
@@ -2284,10 +2284,10 @@
     <t>servicePctOfPriceYear</t>
   </si>
   <si>
-    <t>Три заявления производителей: Ronavi — «от 10 % стоимости проекта в год»; R2Б — обслуживание MARK 2 SE около 20 000 ₽/мес (≈240 000 ₽/год, ≈12,6 % цены 1,9 млн ₽); Вейбот — 30 000 ₽/мес (360 000 ₽/год, 15,6–24 % цены 2,31 и 1,5 млн ₽); цены роботов — из каталога организатора. Берём 12 % между Ronavi и R2Б; тариф Вейбот «под ключ» с еженедельным ТО задаёт верхнюю границу. Применяется, когда у продукта нет своей цены сервиса.</t>
-  </si>
-  <si>
-    <t>Ronavi Robotics, статья «Как считать стоимость владения (TCO)» (ссылка в sourceUrl); R2Б, статья в блоге об окупаемости MARK 2 SE — https://r2b.company/blog/promyshlennyy-robot-uborschik-zachem-on-nuzhen-i-kak-rasschitat-okupaemost; Вейбот Роботикс, «Гарантия и сервис» — https://waybotrobotics.com/guarantee; цены роботов — каталог организатора; https://ronavi-robotics.ru/media/tpost/l8s0fty3m1-kak-schitat-stoimost-vladeniya-tco-logis</t>
+    <t>Три заявления производителей: Ronavi — «от 10 % стоимости проекта в год»; R2Б — обслуживание MARK 2 SE около 20 000 ₽/мес (≈240 000 ₽/год, ≈12,6 % цены 1,9 млн ₽); Вейбот — 30 000 ₽/мес (360 000 ₽/год, 15,6–24 % цены 2,31 и 1,5 млн ₽); цены роботов — из каталога. Берём 12 % между Ronavi и R2Б; тариф Вейбот «под ключ» с еженедельным обслуживанием задаёт верхнюю границу. Применяется, когда у продукта нет своей цены сервиса.</t>
+  </si>
+  <si>
+    <t>Ronavi Robotics, статья «Как считать стоимость владения (TCO)»; R2Б, статья в блоге об окупаемости MARK 2 SE — https://r2b.company/blog/promyshlennyy-robot-uborschik-zachem-on-nuzhen-i-kak-rasschitat-okupaemost; Вейбот Роботикс, «Гарантия и сервис» — https://waybotrobotics.com/guarantee; цены роботов — каталог; https://ronavi-robotics.ru/media/tpost/l8s0fty3m1-kak-schitat-stoimost-vladeniya-tco-logis</t>
   </si>
   <si>
     <t>Ремонт вне сервисного договора в год, доля цены</t>
@@ -2305,7 +2305,7 @@
     <t>consumablesPctOfPriceYear</t>
   </si>
   <si>
-    <t>Организатор включает расходники в OPEX, но величины не даёт. 1 % цены робота в год — оценка для складского AMR без щёток и фильтров; у уборочных роботов доля выше.</t>
+    <t>Легенда демо-набора включает расходники в OPEX, но величины не даёт. 1 % цены робота в год — оценка для складского AMR без щёток и фильтров; у уборочных роботов доля выше.</t>
   </si>
   <si>
     <t>Замена АКБ, раз в</t>
@@ -2314,10 +2314,10 @@
     <t>batteryReplacementYears</t>
   </si>
   <si>
-    <t>Организатор указывает в составе OPEX замену АКБ примерно раз в 3–5 лет. Середина 4 года — наш выбор внутри интервала; если производитель публикует свой срок, берётся он.</t>
-  </si>
-  <si>
-    <t>Датасеты_хакатон.xlsx › легенда «OPEX» замена АКБ ~раз в 3–5 лет</t>
+    <t>Легенда демо-набора указывает в составе OPEX замену АКБ примерно раз в 3–5 лет. Середина 4 года — наш выбор внутри интервала; если производитель публикует свой срок, берётся он.</t>
+  </si>
+  <si>
+    <t>Демо-набор данных › легенда «OPEX» замена АКБ ~раз в 3–5 лет</t>
   </si>
   <si>
     <t>Стоимость комплекта АКБ, доля цены робота</t>
@@ -2356,7 +2356,7 @@
     <t>connectivityRubPerUnitYear</t>
   </si>
   <si>
-    <t>ТЗ включает связь в OPEX, но ни организатор, ни производители цену не дают. 1 000 ₽ в месяц на робот (SIM-карта или доля обслуживания Wi-Fi, мониторинг) — оценка.</t>
+    <t>Связь входит в OPEX, но ни демо-набор, ни производители цену не дают. 1 000 ₽ в месяц на робот (SIM-карта или доля обслуживания Wi-Fi, мониторинг) — оценка.</t>
   </si>
   <si>
     <t>Оценка ставки RaaS в месяц, доля цены робота</t>
@@ -2368,10 +2368,10 @@
     <t>доля в месяц</t>
   </si>
   <si>
-    <t>Медиана отношения опубликованной месячной ставки аренды к цене робота из каталога организатора по четырём тарифам: Ronavi H1500 (от 100 000 ₽ при 2,7 млн ₽), R2Б MARK 2 SE (от 100 000 ₽ при 1,9 млн ₽), Клинботикс 400 PRO (100 000 ₽ при 1,5 млн ₽), Клинботикс 600 (120 000 ₽ при 2,31 млн ₽); у Клинботикс это ставка со второго месяца, первый месяц дороже (260 000 и 400 000 ₽). Подставляется только по явному действию пользователя, с пометкой «оценка» и риском RAAS_ESTIMATE.</t>
-  </si>
-  <si>
-    <t>Тарифы аренды: Ronavi — https://robotrends.ru/robopedia/ronavi-robotics («от 100 тысяч рублей в месяц за одного робота»); R2Б — https://r2b.company/blog/promyshlennyy-robot-uborschik-zachem-on-nuzhen-i-kak-rasschitat-okupaemost, https://r2b.company/rent; Вейбот Роботикс (Клинботикс), «Покупка и аренда» — https://waybotrobotics.com/buy-rent; цены роботов — каталог организатора; Формула: медиана(100 000/2 700 000; 100 000/1 900 000; 100 000/1 500 000; 120 000/2 310 000)</t>
+    <t>Медиана отношения опубликованной месячной ставки RaaS к цене робота из каталога по четырём тарифам: Ronavi H1500 (от 100 000 ₽ при 2,7 млн ₽), R2Б MARK 2 SE (от 100 000 ₽ при 1,9 млн ₽), Клинботикс 400 PRO (100 000 ₽ при 1,5 млн ₽), Клинботикс 600 (120 000 ₽ при 2,31 млн ₽); у Клинботикс это ставка со второго месяца, первый месяц дороже (260 000 и 400 000 ₽). Подставляется только по явному действию пользователя, с пометкой «оценка» и предупреждением в рисках сценария.</t>
+  </si>
+  <si>
+    <t>Ставки RaaS: Ronavi — https://robotrends.ru/robopedia/ronavi-robotics («от 100 тысяч рублей в месяц за одного робота»); R2Б — https://r2b.company/blog/promyshlennyy-robot-uborschik-zachem-on-nuzhen-i-kak-rasschitat-okupaemost, https://r2b.company/rent; Вейбот Роботикс (Клинботикс), «Покупка и аренда» — https://waybotrobotics.com/buy-rent; цены роботов — каталог; Формула: медиана(100 000/2 700 000; 100 000/1 900 000; 100 000/1 500 000; 120 000/2 310 000)</t>
   </si>
   <si>
     <t>Финансы</t>
@@ -2383,7 +2383,7 @@
     <t>Наш выбор</t>
   </si>
   <si>
-    <t>Ставка дисконтирования 12 % — наш выбор, а не цитата. Отражает стоимость денег для частного покупателя оборудования в рублёвой экономике: она обязана быть выше безрисковой ставки, потому что проект автоматизации рискованнее гособлигаций. Правильное значение зависит от структуры капитала конкретного покупателя, поэтому спорить с ним нужно подстановкой своей ставки, а не нашей защитой этой.</t>
+    <t>Ставка дисконтирования 12 % — наш выбор, а не цитата. Отражает стоимость денег для частного покупателя оборудования в рублёвой экономике: она обязана быть выше безрисковой ставки, потому что проект автоматизации рискованнее гособлигаций. Правильное значение зависит от структуры капитала конкретного покупателя: если 12 % вам не подходит, подставьте свою ставку.</t>
   </si>
   <si>
     <t>Срок службы робота (если производитель не публикует)</t>
@@ -2401,13 +2401,13 @@
     <t>tcoMinYears</t>
   </si>
   <si>
-    <t>ТЗ</t>
-  </si>
-  <si>
-    <t>ТЗ требует считать TCO на горизонте не менее пяти лет, поэтому TCO считается за max(горизонт проекта, 5 лет) даже при горизонте окупаемости 3 года. Верхняя граница 30 лет — не норматив, а защита от опечатки при правке: денежные потоки считаются по годам.</t>
-  </si>
-  <si>
-    <t>ТЗ §3.5.2</t>
+    <t>Методика</t>
+  </si>
+  <si>
+    <t>Методика требует считать TCO на горизонте не менее пяти лет, поэтому TCO считается за max(горизонт расчёта, 5 лет) даже при горизонте 3 года. Верхняя граница 30 лет защищает от опечатки при правке: денежные потоки считаются по годам.</t>
+  </si>
+  <si>
+    <t>Методика расчёта › горизонт TCO</t>
   </si>
   <si>
     <t>Граница «быстрой» окупаемости</t>
@@ -2416,10 +2416,10 @@
     <t>paybackBandFastYears</t>
   </si>
   <si>
-    <t>ТЗ предлагает настраиваемые интервалы окупаемости «до 3 лет, 3–5 лет и более 5 лет» и запрещает строить рекомендацию только на жёстком пороге; интервал — описание, не критерий.</t>
-  </si>
-  <si>
-    <t>ТЗ §3.5.7</t>
+    <t>Методика задаёт настраиваемые интервалы окупаемости «до 3 лет, 3–5 лет и более 5 лет» и не строит рекомендацию только на жёстком пороге; интервал лишь описывает результат.</t>
+  </si>
+  <si>
+    <t>Методика расчёта › интервалы окупаемости</t>
   </si>
   <si>
     <t>Граница «долгой» окупаемости</t>
@@ -2428,16 +2428,16 @@
     <t>paybackBandSlowYears</t>
   </si>
   <si>
-    <t>Верхняя граница среднего интервала из примера ТЗ «3–5 лет»; окупаемость дольше описывается как «долгая», но сценарий не отбрасывается. Если правка сделает её меньше границы «быстрой», resolveNorms поднимет её до этой границы, чтобы интервалы не перевернулись.</t>
-  </si>
-  <si>
-    <t>Шаг чувствительности, если нет диапазона организатора</t>
+    <t>Верхняя граница среднего интервала «3–5 лет»; окупаемость дольше описывается как «долгая», но сценарий не отбрасывается. Если правка сделает её меньше границы «быстрой», платформа поднимет её до этой границы, чтобы интервалы не перевернулись.</t>
+  </si>
+  <si>
+    <t>Шаг чувствительности, если нет типового диапазона</t>
   </si>
   <si>
     <t>sensitivityDeltaPct</t>
   </si>
   <si>
-    <t>ТЗ требует чувствительность минимум к трём параметрам, но ширину не задаёт. Где у организатора есть min/max, берутся они; иначе ±20 % — наш выбор, достаточно широкий, чтобы показать смену знака, и не выходящий за правдоподобные значения.</t>
+    <t>Чувствительность считается минимум к трём параметрам, но её ширина не задана. Где есть типовой диапазон (min/max), берётся он; иначе ±20 % — наш выбор, достаточно широкий, чтобы показать смену знака, и не выходящий за правдоподобные значения.</t>
   </si>
   <si>
     <t>Минимальная доля обслуженных заданий для подтверждения</t>
@@ -2494,7 +2494,7 @@
     <t>chargeStartSoc</t>
   </si>
   <si>
-    <t>Робот уходит на зарядку при 20 % заряда. Производители порог не публикуют, и он настраивается в системе управления парком; значение — оценка типовой настройки. Порог возврата всегда выше порога ухода минимум на 5 п.п. (см. resolveNorms), поэтому верхняя граница 0,95.</t>
+    <t>Робот уходит на зарядку при 20 % заряда. Производители порог не публикуют, и он настраивается в системе управления парком; значение — оценка типовой настройки. Порог возврата всегда выше порога ухода минимум на 5 п.п., поэтому верхняя граница 0,95.</t>
   </si>
   <si>
     <t>Заряд, при котором робот возвращается в работу</t>
@@ -2503,7 +2503,7 @@
     <t>chargeStopSoc</t>
   </si>
   <si>
-    <t>Робот возвращается в работу при 90 % заряда: последние проценты заряжаются медленнее. Порог настраивается в системе управления парком; значение — оценка типовой настройки. Если правка сделает его не выше порога ухода, resolveNorms поднимет его до порога ухода + 5 п.п., иначе робот метался бы между работой и зарядкой.</t>
+    <t>Робот возвращается в работу при 90 % заряда: последние проценты заряжаются медленнее. Порог настраивается в системе управления парком; значение — оценка типовой настройки. Если правка сделает его не выше порога ухода, платформа поднимет его до порога ухода + 5 п.п., иначе робот метался бы между работой и зарядкой.</t>
   </si>
   <si>
     <t>Подбор</t>
@@ -2515,7 +2515,7 @@
     <t>scoreWeightEcon</t>
   </si>
   <si>
-    <t>Экономика — главный вопрос заказчика, поэтому NPV покупки весит больше всего. Веса балла — наш выбор, а не факт; вклад каждого фактора показывается отдельно, чтобы с ранжированием можно было спорить по существу.</t>
+    <t>Экономика — главный вопрос заказчика, поэтому NPV покупки весит больше всего. Веса балла — наш выбор; вклад каждого фактора показывается отдельно, чтобы с ранжированием можно было спорить по существу.</t>
   </si>
   <si>
     <t>Вес фактора «Данные» в балле подбора</t>
@@ -2533,7 +2533,7 @@
     <t>scoreWeightMaturity</t>
   </si>
   <si>
-    <t>Серийная эксплуатация надёжнее пилота: статус из каталога организатора учитывается отдельным фактором. Вес — наш выбор.</t>
+    <t>Серийная эксплуатация надёжнее пилота: статус из каталога учитывается отдельным фактором. Вес — наш выбор.</t>
   </si>
   <si>
     <t>Вес фактора «Запас» в балле подбора</t>
@@ -2551,7 +2551,7 @@
     <t>scoreWeightCases</t>
   </si>
   <si>
-    <t>Наличие опубликованных внедрений: слабый, но полезный сигнал зрелости, поэтому вес наименьший. Вес — наш выбор; сумма весов равна 1. Если после правки сумма отличается от 1, resolveNorms делит каждый вес на сумму, и балл остаётся в пределах 0–100; если все веса обнулены, берутся веса по умолчанию.</t>
+    <t>Наличие опубликованных внедрений: слабый, но полезный сигнал зрелости, поэтому вес наименьший. Вес — наш выбор; сумма весов равна 1. Если после правки сумма отличается от 1, платформа делит каждый вес на сумму, и балл остаётся в пределах 0–100; если все веса обнулены, берутся веса по умолчанию.</t>
   </si>
   <si>
     <t>Характеристика</t>
@@ -2566,7 +2566,7 @@
     <t>Ссылка</t>
   </si>
   <si>
-    <t>Где у организатора</t>
+    <t>Где в источнике</t>
   </si>
   <si>
     <t>Производитель</t>
@@ -2578,7 +2578,7 @@
     <t>2026-09-22</t>
   </si>
   <si>
-    <t>catalog_export_v4.csv › №9</t>
+    <t>Каталог › №9</t>
   </si>
   <si>
     <t>Наименование (модель)</t>
@@ -2725,13 +2725,13 @@
     <t>Подтверждение</t>
   </si>
   <si>
-    <t>3 из 23 подтверждены; строка свода: нет</t>
+    <t>3 из 23 подтверждены; строка сводной таблицы исследования: нет</t>
   </si>
   <si>
     <t>ООО "Ронави Роботикс"</t>
   </si>
   <si>
-    <t>catalog_export_v4.csv › №1, 66</t>
+    <t>Каталог › №1, 66</t>
   </si>
   <si>
     <t>Внутрискладская логистика; Внутрипроизводственная логистика</t>
@@ -2743,7 +2743,7 @@
     <t>в эксплуатации</t>
   </si>
   <si>
-    <t>Примеры решений › Склад, Аэропорт › Ronavi H1500</t>
+    <t>Подборка примеров › Склад, Аэропорт › Ronavi H1500</t>
   </si>
   <si>
     <t>1044 × 654 × 380</t>
@@ -2821,9 +2821,6 @@
     <t>покупка, лизинг, аренда / RaaS</t>
   </si>
   <si>
-    <t>Ставка RaaS (аренда)</t>
-  </si>
-  <si>
     <t>от 100 000 ₽/мес</t>
   </si>
   <si>
@@ -2839,7 +2836,7 @@
     <t>Внедрено 48 роботов на складах ГК «Восток-Сервис» для транспортировки грузов между зонами хранения. В результате производительность выросла вдвое - с 4 до 8 тысяч отгрузок за смену, количество ошибок…</t>
   </si>
   <si>
-    <t>9 из 31 подтверждены; строка свода: да</t>
+    <t>9 из 31 подтверждены; строка сводной таблицы исследования: да</t>
   </si>
   <si>
     <t>Источники параметров объекта — на листе «Параметры объекта», нормативов — на листе «Нормативы и допущения».</t>
@@ -2872,22 +2869,22 @@
     <t>Версии</t>
   </si>
   <si>
-    <t>Версия данных проекта (хэш снимков продуктов и нормативов)</t>
-  </si>
-  <si>
-    <t>Датасеты организатора в этой сборке</t>
+    <t>Версия данных проекта (по снимкам продуктов и нормативов)</t>
+  </si>
+  <si>
+    <t>Текущий демо-набор данных</t>
   </si>
   <si>
     <t>2026-09-22#4be0fac8</t>
   </si>
   <si>
-    <t>Каталог организатора в этой сборке</t>
+    <t>Текущий каталог</t>
   </si>
   <si>
     <t>2026-09-22#da43c64c</t>
   </si>
   <si>
-    <t>«Примеры решений» организатора в этой сборке</t>
+    <t>Текущая подборка примеров решений</t>
   </si>
   <si>
     <t>2026-09-22#6e738822</t>
@@ -2896,7 +2893,7 @@
     <t>Исследование открытых источников</t>
   </si>
   <si>
-    <t>svod 2026-09-23 + found_batch1-6@2026-09-23T21:13:10Z</t>
+    <t>сводная таблица от 23.09.2026 и 6 пакетов находок, зафиксировано 23.09.2026 21:13 UTC</t>
   </si>
   <si>
     <t>Как устроен файл</t>
@@ -2932,6 +2929,9 @@
     <t>ч/сут; ч/год</t>
   </si>
   <si>
+    <t>базовые данные</t>
+  </si>
+  <si>
     <t>Суточный спрос процесса</t>
   </si>
   <si>
@@ -2980,6 +2980,9 @@
     <t>Nточн = λпик / (thrэфф × U × A) × (1 + резерв); N = значение, заданное вами, иначе max(1; ⌈Nточн⌉)</t>
   </si>
   <si>
+    <t>типовая расчётная зависимость</t>
+  </si>
+  <si>
     <t>Доля пикового спроса, которую закрывает парк</t>
   </si>
   <si>
@@ -2989,7 +2992,7 @@
     <t>Число зарядных станций</t>
   </si>
   <si>
-    <t>C = max(1; ⌈N × tзар / (автономность × 60 + tзар) × kзапас⌉); без данных о зарядке C = max(1; ⌈N / роботов на станцию⌉); для стационарных систем C = 0</t>
+    <t>C = max(1; ⌈N × tзар / (автономность × 60 + tзар) × kзапас⌉); без данных о зарядке C = max(1; ⌈N / роботов на станцию⌉); для стационарных решений C = 0</t>
   </si>
   <si>
     <t>Годовая стоимость одной ставки</t>
@@ -2998,7 +3001,7 @@
     <t>c = зарплата × 12 × коэффициент начислений на ФОТ</t>
   </si>
   <si>
-    <t>ФОТ персонала процесса (как есть)</t>
+    <t>ФОТ персонала процесса («Как есть»)</t>
   </si>
   <si>
     <t>ФОТбаз = численность × c</t>
@@ -3052,10 +3055,7 @@
     <t>ROI = Σ CFt (t = 1…H) / CAPEX × 100 %, при CAPEX &gt; 0</t>
   </si>
   <si>
-    <t>Чистый ROI</t>
-  </si>
-  <si>
-    <t>ROIчист = ROI по ТЗ − 100 % (доход сверх возврата вложений)</t>
+    <t>ROIчист = ROI валовый − 100 % (доход сверх возврата вложений)</t>
   </si>
   <si>
     <t>Чистая приведённая стоимость (NPV)</t>
@@ -3109,10 +3109,13 @@
     <t>Длина плеча перевозки оценена по типовой планировке, построенной из площади активной зоны и ширины проходов, а не по чертежу объекта.</t>
   </si>
   <si>
-    <t>Стоимость существующего парка погрузчиков и его обслуживания в датасете организатора не задана, поэтому её экономия в эффект не входит — эффект занижен, оценка консервативна.</t>
-  </si>
-  <si>
-    <t>Состав подписки RaaS принят по допущению: оборудование, зарядные станции, ПО, сервис, ремонт, расходники и замена АКБ входят в ставку; интеграция и обучение оплачиваются отдельно. Состав проверяется по договору с поставщиком.</t>
+    <t>Стоимость существующего парка погрузчиков и его обслуживания в исходных данных не задана, поэтому её экономия в эффект не входит — эффект занижен, оценка консервативна.</t>
+  </si>
+  <si>
+    <t>Состав подписки RaaS принят по допущению: оборудование, зарядные станции, ПО, сервис, ремонт, расходники и замена АКБ входят в ставку; интеграция и обучение оплачиваются отдельно. Состав нужно проверить по договору с поставщиком.</t>
+  </si>
+  <si>
+    <t>Цены оборудования из каталога приняты с НДС. Пусконаладка и интеграция в цену не входят и считаются отдельными статьями CAPEX; доставка отдельной статьёй не выделена и учитывается только в резерве CAPEX (10 %).</t>
   </si>
   <si>
     <t>Часть статей CAPEX и OPEX — оценки или нормативы-аналоги другого производителя (пометка «аналог: …»); у каждой такой статьи показано происхождение и обоснование.</t>
@@ -3127,7 +3130,7 @@
     <t>Остаточная стоимость оборудования на конце горизонта не учитывается: докупка оборудования в год окончания срока службы входит в поток полностью, если горизонт длиннее срока службы, и не входит, если горизонт равен сроку службы. Поэтому NPV покупки скачком снижается, когда горизонт превышает срок службы (при сроке службы 7 лет — между горизонтами 7 и 8 лет), и вывод по горизонту может меняться не монотонно.</t>
   </si>
   <si>
-    <t>Экономика рассчитывается для перемещения паллет на складе; остальные процессы и типы объектов показаны на уровне параметров, подбора и доступных решений (прототип, ТЗ §5.7).</t>
+    <t>Экономика рассчитывается для перемещения паллет на складе; остальные процессы и типы объектов показаны на уровне параметров, подбора и доступных решений (прототип).</t>
   </si>
 </sst>
 </file>
@@ -5080,7 +5083,7 @@
       <c r="J12" s="7" t="s">
         <v>712</v>
       </c>
-      <c r="K12" s="7" t="s">
+      <c r="K12" s="3" t="s">
         <v>713</v>
       </c>
     </row>
@@ -7082,7 +7085,7 @@
       <c r="B27" s="3" t="s">
         <v>899</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C27" s="7" t="s">
         <v>900</v>
       </c>
       <c r="D27" s="3" t="s">
@@ -7808,10 +7811,10 @@
         <v>311</v>
       </c>
       <c r="B55" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="C55" s="3" t="s">
         <v>932</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>933</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>508</v>
@@ -7823,7 +7826,7 @@
         <v>855</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>35</v>
@@ -7837,7 +7840,7 @@
         <v>761</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>508</v>
@@ -7849,7 +7852,7 @@
         <v>855</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>35</v>
@@ -7889,7 +7892,7 @@
         <v>895</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>504</v>
@@ -7966,8 +7969,8 @@
       <c r="B61" s="3" t="s">
         <v>899</v>
       </c>
-      <c r="C61" s="3" t="s">
-        <v>938</v>
+      <c r="C61" s="7" t="s">
+        <v>937</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>286</v>
@@ -7987,7 +7990,7 @@
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
   </sheetData>
@@ -8044,33 +8047,33 @@
         <v>845</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>61</v>
       </c>
       <c r="D1" s="5" t="s">
+        <v>940</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>941</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>942</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>943</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>944</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>116</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
   </sheetData>
@@ -8081,7 +8084,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D80"/>
+  <dimension ref="A1:D81"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="44" customWidth="1"/>
@@ -8092,12 +8095,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -8126,7 +8129,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>12</v>
@@ -8134,39 +8137,39 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>949</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>950</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>951</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
+        <v>951</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>952</v>
       </c>
-      <c r="B9" s="3" t="s">
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>953</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
+      <c r="B10" s="3" t="s">
         <v>954</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>955</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
+        <v>955</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>956</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>957</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -8174,7 +8177,7 @@
         <v>126</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -8182,7 +8185,7 @@
         <v>126</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -8190,7 +8193,7 @@
         <v>126</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -8198,12 +8201,12 @@
         <v>126</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -8214,24 +8217,24 @@
         <v>497</v>
       </c>
       <c r="C20" s="5" t="s">
+        <v>963</v>
+      </c>
+      <c r="D20" s="5" t="s">
         <v>964</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>965</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="B21" s="7" t="s">
         <v>966</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="C21" s="3" t="s">
         <v>967</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>968</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>624</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -8259,7 +8262,7 @@
         <v>975</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>624</v>
+        <v>968</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -8315,15 +8318,15 @@
         <v>135</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>794</v>
+        <v>985</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>629</v>
@@ -8334,10 +8337,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>135</v>
@@ -8348,41 +8351,41 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>642</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>624</v>
+        <v>968</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>642</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>794</v>
+        <v>985</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>972</v>
@@ -8393,13 +8396,13 @@
         <v>568</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>642</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>794</v>
+        <v>985</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -8407,7 +8410,7 @@
         <v>565</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>642</v>
@@ -8427,7 +8430,7 @@
         <v>638</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>794</v>
+        <v>985</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -8441,7 +8444,7 @@
         <v>638</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>794</v>
+        <v>985</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -8455,7 +8458,7 @@
         <v>638</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>794</v>
+        <v>985</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -8469,7 +8472,7 @@
         <v>638</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>794</v>
+        <v>985</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -8483,7 +8486,7 @@
         <v>638</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>794</v>
+        <v>985</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -8497,7 +8500,7 @@
         <v>638</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>794</v>
+        <v>985</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -8511,12 +8514,12 @@
         <v>638</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>794</v>
+        <v>985</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>526</v>
@@ -8525,7 +8528,7 @@
         <v>638</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>624</v>
+        <v>968</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -8533,13 +8536,13 @@
         <v>31</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>638</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>794</v>
+        <v>985</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -8553,7 +8556,7 @@
         <v>642</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>794</v>
+        <v>985</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -8567,7 +8570,7 @@
         <v>642</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>794</v>
+        <v>985</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -8581,7 +8584,7 @@
         <v>642</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>794</v>
+        <v>985</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -8595,7 +8598,7 @@
         <v>642</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>794</v>
+        <v>985</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -8609,7 +8612,7 @@
         <v>642</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>794</v>
+        <v>985</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -8623,7 +8626,7 @@
         <v>642</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>624</v>
+        <v>968</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -8637,7 +8640,7 @@
         <v>642</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>794</v>
+        <v>985</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -8651,7 +8654,7 @@
         <v>642</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>624</v>
+        <v>968</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -8665,7 +8668,7 @@
         <v>642</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>794</v>
+        <v>985</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -8679,15 +8682,15 @@
         <v>642</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>794</v>
+        <v>985</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="7" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>642</v>
@@ -8707,49 +8710,49 @@
         <v>642</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>794</v>
+        <v>985</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>642</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>794</v>
+        <v>985</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>642</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>794</v>
+        <v>985</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>272</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>794</v>
+        <v>985</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -8757,18 +8760,18 @@
         <v>41</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>183</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>794</v>
+        <v>985</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>1009</v>
+        <v>42</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>1010</v>
@@ -8819,7 +8822,7 @@
         <v>638</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>794</v>
+        <v>985</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -8847,7 +8850,7 @@
         <v>638</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>624</v>
+        <v>968</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -8955,8 +8958,16 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80" s="15" t="s">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" s="15" t="s">
         <v>112</v>
       </c>
     </row>
@@ -16906,13 +16917,13 @@
         <v>630</v>
       </c>
       <c r="H12" s="18">
-        <v>-499996.67670560814</v>
+        <v>-499996.67670561</v>
       </c>
       <c r="I12" s="18">
         <v>-9834465.361604953</v>
       </c>
       <c r="J12" s="18">
-        <v>9334468.684899345</v>
+        <v>9334468.684899343</v>
       </c>
       <c r="K12" s="19">
         <v>4.130191253812285</v>
@@ -17846,13 +17857,13 @@
         <v>630</v>
       </c>
       <c r="H32" s="18">
-        <v>7864180.073133251</v>
+        <v>7864180.073133249</v>
       </c>
       <c r="I32" s="18">
         <v>-2171492.753580261</v>
       </c>
       <c r="J32" s="18">
-        <v>10035672.826713512</v>
+        <v>10035672.82671351</v>
       </c>
       <c r="K32" s="19">
         <v>3.271423708965064</v>
